--- a/out/Attention-S4_repeat_5_000007.xlsx
+++ b/out/Attention-S4_repeat_5_000007.xlsx
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.3</v>
+        <v>-1.260392056209815</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.3</v>
+        <v>-1.260392056209815</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.3</v>
+        <v>-1.260392056209815</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.3</v>
+        <v>-1.260392056209815</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.3</v>
+        <v>-1.260392056209815</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.3</v>
+        <v>-1.260392056209815</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.3</v>
+        <v>-1.260392056209815</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.3</v>
+        <v>-1.260392056209815</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.3</v>
+        <v>-1.260392056209815</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.3</v>
+        <v>-1.260392056209815</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.3</v>
+        <v>-1.260392056209815</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.3</v>
+        <v>-1.260392056209815</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.3</v>
+        <v>-1.260392056209815</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.3</v>
+        <v>-1.260392056209815</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.3</v>
+        <v>-1.260392056209815</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.3</v>
+        <v>-1.260392056209815</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.3</v>
+        <v>-1.260392056209815</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.3</v>
+        <v>-1.260392056209815</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.3</v>
+        <v>-1.260392056209815</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.3</v>
+        <v>-1.260392056209815</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.3</v>
+        <v>-1.260392056209815</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.3</v>
+        <v>-1.260392056209815</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.3</v>
+        <v>-1.260392056209815</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.3</v>
+        <v>-1.260392056209815</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.3</v>
+        <v>-1.260392056209815</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.3</v>
+        <v>-1.260392056209815</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.3</v>
+        <v>-1.260392056209815</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.3</v>
+        <v>-1.260392056209815</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.3</v>
+        <v>-1.260392056209815</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.3</v>
+        <v>-1.260392056209815</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.3</v>
+        <v>-1.260392056209815</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.3</v>
+        <v>-1.260392056209815</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.3</v>
+        <v>-1.260392056209815</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.3</v>
+        <v>-1.260392056209815</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.3</v>
+        <v>-1.260392056209815</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.3</v>
+        <v>2.340833119445856</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.3</v>
+        <v>2.340833119445856</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,10 +31949,10 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.3</v>
+        <v>2.340833119445856</v>
       </c>
       <c r="JC39" t="n">
-        <v>-7.712256331345998e-05</v>
+        <v>-0.0002785075233038515</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>0.889109252280405</v>
+        <v>3.210780338795037</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32744,10 +32744,10 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.3</v>
+        <v>2.340833119445856</v>
       </c>
       <c r="JC40" t="n">
-        <v>1.779592907008404</v>
+        <v>6.426524116103795</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.1333258984963202</v>
+        <v>0.4814708343729628</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33539,10 +33539,10 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.3</v>
+        <v>2.340833119445856</v>
       </c>
       <c r="JC41" t="n">
-        <v>1.155942144807108</v>
+        <v>4.174376031103803</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.1667007545622656</v>
+        <v>0.6019952034443758</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34334,10 +34334,10 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.3</v>
+        <v>2.340833119445856</v>
       </c>
       <c r="JC42" t="n">
-        <v>1.356038928517799</v>
+        <v>4.896972132748714</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.2389645784281521</v>
+        <v>0.8629572692344619</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.3</v>
+        <v>2.340833119445856</v>
       </c>
       <c r="JC43" t="n">
-        <v>1.667361733030028</v>
+        <v>6.021231412498176</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.2556451129256772</v>
+        <v>0.9231933436904723</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.3</v>
+        <v>-1.260392056209815</v>
       </c>
       <c r="JC44" t="n">
-        <v>1.939704871897068</v>
+        <v>7.004725542514382</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.2709315542955592</v>
+        <v>0.9783996038219227</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.3</v>
+        <v>-1.260392056209815</v>
       </c>
       <c r="JC45" t="n">
-        <v>2.225943688836998</v>
+        <v>8.038400568431435</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1222670373213373</v>
+        <v>0.4415335441710621</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.3</v>
+        <v>-1.260392056209815</v>
       </c>
       <c r="JC46" t="n">
-        <v>2.19931958941948</v>
+        <v>7.942255006768041</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.05904874746033055</v>
+        <v>0.2132405208634418</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.3</v>
+        <v>-1.260392056209815</v>
       </c>
       <c r="JC47" t="n">
-        <v>2.19505546025556</v>
+        <v>7.926856281692531</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.02813558306727647</v>
+        <v>0.1016021467214458</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.3</v>
+        <v>-1.260392056209815</v>
       </c>
       <c r="JC48" t="n">
-        <v>2.192229698691393</v>
+        <v>7.916651938456775</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.008333563627179606</v>
+        <v>0.03010437054442755</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.3</v>
+        <v>-1.260392056209815</v>
       </c>
       <c r="JC49" t="n">
-        <v>2.180734450292196</v>
+        <v>7.875149080244426</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.005510641582937633</v>
+        <v>0.01991291850757113</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.3</v>
+        <v>-1.260392056209815</v>
       </c>
       <c r="JC50" t="n">
-        <v>2.18341892269172</v>
+        <v>7.884854827986227</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.002817967231921131</v>
+        <v>0.01018975897174445</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.3</v>
+        <v>-1.260392056209815</v>
       </c>
       <c r="JC51" t="n">
-        <v>2.183540957973626</v>
+        <v>7.885308516381392</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.001439560167255453</v>
+        <v>0.005209509872044073</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.3</v>
+        <v>-1.260392056209815</v>
       </c>
       <c r="JC52" t="n">
-        <v>2.183599447234295</v>
+        <v>7.885532719861526</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0005376864856202011</v>
+        <v>0.001955331935503934</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.3</v>
+        <v>-1.260392056209815</v>
       </c>
       <c r="JC53" t="n">
-        <v>2.183234922977324</v>
+        <v>7.884229673235657</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0002911771458358382</v>
+        <v>0.00106338274054989</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.3</v>
+        <v>-1.260392056209815</v>
       </c>
       <c r="JC54" t="n">
-        <v>2.183278531161338</v>
+        <v>7.884400082937997</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0001372566611499408</v>
+        <v>0.0005099850079617968</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.3</v>
+        <v>-1.260392056209815</v>
       </c>
       <c r="JC55" t="n">
-        <v>2.183262475273386</v>
+        <v>7.884355169122595</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>8.355596056915365e-05</v>
+        <v>0.000313801458048953</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.3</v>
+        <v>-1.260392056209815</v>
       </c>
       <c r="JC56" t="n">
-        <v>2.183291468911106</v>
+        <v>7.884472546218391</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>4.132161208684532e-05</v>
+        <v>0.0001617578035126432</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.3</v>
+        <v>-1.260392056209815</v>
       </c>
       <c r="JC57" t="n">
-        <v>2.183290504722986</v>
+        <v>7.884482075141158</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>1.698004887727391e-05</v>
+        <v>7.592654359359939e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.3</v>
+        <v>-1.260392056209815</v>
       </c>
       <c r="JC58" t="n">
-        <v>2.183284113910244</v>
+        <v>7.884472066026267</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>9.070610155389825e-06</v>
+        <v>4.616585511050847e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.3</v>
+        <v>-1.260392056209815</v>
       </c>
       <c r="JC59" t="n">
-        <v>2.1832855457952</v>
+        <v>7.884489715489589</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>1.993667665820105e-06</v>
+        <v>1.831222555273368e-05</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.3</v>
+        <v>-1.260392056209815</v>
       </c>
       <c r="JC60" t="n">
-        <v>2.18327917324003</v>
+        <v>7.884480026634181</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-1.911892527543644e-06</v>
+        <v>5.293691574854516e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.3</v>
+        <v>-1.260392056209815</v>
       </c>
       <c r="JC61" t="n">
-        <v>2.183273351047698</v>
+        <v>7.884472149587268</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-3.887371769088796e-06</v>
+        <v>5.63141154556023e-07</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.3</v>
+        <v>-1.260392056209815</v>
       </c>
       <c r="JC62" t="n">
-        <v>2.183268599772485</v>
+        <v>7.884468059774779</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-4.031182895915095e-06</v>
+        <v>-2.093548687745288e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.3</v>
+        <v>-1.260392056209815</v>
       </c>
       <c r="JC63" t="n">
-        <v>2.183263310624922</v>
+        <v>7.884462192332094</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0</v>
+        <v>-4.053889915940302e-06</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.3</v>
+        <v>-1.260392056209815</v>
       </c>
       <c r="JC64" t="n">
-        <v>2.183263287890621</v>
+        <v>7.884457122976726</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0</v>
+        <v>-3.735991635587426e-06</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.3</v>
+        <v>-1.260392056209815</v>
       </c>
       <c r="JC65" t="n">
-        <v>2.183263606170838</v>
+        <v>7.884452758002758</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.3</v>
+        <v>-1.260392056209815</v>
       </c>
       <c r="JC66" t="n">
-        <v>2.183264697417295</v>
+        <v>7.884453849249214</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.3</v>
+        <v>-1.260392056209815</v>
       </c>
       <c r="JC67" t="n">
-        <v>2.183264007810159</v>
+        <v>7.884453159642078</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.3</v>
+        <v>-1.260392056209815</v>
       </c>
       <c r="JC68" t="n">
-        <v>2.183264038122561</v>
+        <v>7.88445318995448</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.3</v>
+        <v>-1.260392056209815</v>
       </c>
       <c r="JC69" t="n">
-        <v>2.18326384867005</v>
+        <v>7.88445300050197</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.3</v>
+        <v>-1.260392056209815</v>
       </c>
       <c r="JC70" t="n">
-        <v>2.183263901716753</v>
+        <v>7.884453053548673</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.3</v>
+        <v>-1.260392056209815</v>
       </c>
       <c r="JC71" t="n">
-        <v>2.183263954763456</v>
+        <v>7.884453106595375</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.3</v>
+        <v>-1.260392056209815</v>
       </c>
       <c r="JC72" t="n">
-        <v>2.183263916872954</v>
+        <v>7.884453068704874</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.3</v>
+        <v>-1.260392056209815</v>
       </c>
       <c r="JC73" t="n">
-        <v>2.183263788045247</v>
+        <v>7.884452939877168</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.3</v>
+        <v>2.340833119445856</v>
       </c>
       <c r="JC74" t="n">
-        <v>2.18326364406134</v>
+        <v>7.884452795893259</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.3</v>
+        <v>2.340833119445856</v>
       </c>
       <c r="JC75" t="n">
-        <v>2.183263484921231</v>
+        <v>7.884452636753151</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.3</v>
+        <v>-0.6603920562098147</v>
       </c>
       <c r="JC76" t="n">
-        <v>2.183263537967934</v>
+        <v>7.884452689799854</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.3</v>
+        <v>-0.6603920562098147</v>
       </c>
       <c r="JC77" t="n">
-        <v>2.183263484921231</v>
+        <v>7.884452636753151</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.3</v>
+        <v>-1.260392056209815</v>
       </c>
       <c r="JC78" t="n">
-        <v>2.183263484921231</v>
+        <v>7.884452636753151</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.3</v>
+        <v>-1.260392056209815</v>
       </c>
       <c r="JC79" t="n">
-        <v>2.183263303046822</v>
+        <v>7.884452454878742</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.3</v>
+        <v>-1.260392056209815</v>
       </c>
       <c r="JC80" t="n">
-        <v>2.183263469765031</v>
+        <v>7.884452621596951</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.3</v>
+        <v>2.340833119445856</v>
       </c>
       <c r="JC81" t="n">
-        <v>2.183263666795641</v>
+        <v>7.884452818627561</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.3</v>
+        <v>2.340833119445856</v>
       </c>
       <c r="JC82" t="n">
-        <v>2.183263507655533</v>
+        <v>7.884452659487453</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.3</v>
+        <v>2.340833119445856</v>
       </c>
       <c r="JC83" t="n">
-        <v>2.183263545546035</v>
+        <v>7.884452697377954</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.3</v>
+        <v>2.340833119445856</v>
       </c>
       <c r="JC84" t="n">
-        <v>2.183263742576645</v>
+        <v>7.884452894408565</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.3</v>
+        <v>-0.6603920562098147</v>
       </c>
       <c r="JC85" t="n">
-        <v>2.183263719842344</v>
+        <v>7.884452871674264</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.3</v>
+        <v>-1.260392056209815</v>
       </c>
       <c r="JC86" t="n">
-        <v>2.183263568280336</v>
+        <v>7.884452720112255</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.3</v>
+        <v>-1.260392056209815</v>
       </c>
       <c r="JC87" t="n">
-        <v>2.183263492499332</v>
+        <v>7.884452644331252</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.3</v>
+        <v>1.740833119445856</v>
       </c>
       <c r="JC88" t="n">
-        <v>2.183263591014637</v>
+        <v>7.884452742846556</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.3</v>
+        <v>2.340833119445856</v>
       </c>
       <c r="JC89" t="n">
-        <v>2.183263598592738</v>
+        <v>7.884452750424657</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.3</v>
+        <v>2.340833119445856</v>
       </c>
       <c r="JC90" t="n">
-        <v>2.183263863826252</v>
+        <v>7.88445301565817</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.3</v>
+        <v>2.340833119445856</v>
       </c>
       <c r="JC91" t="n">
-        <v>2.183263568280336</v>
+        <v>7.884452720112255</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.3</v>
+        <v>2.340833119445856</v>
       </c>
       <c r="JC92" t="n">
-        <v>2.183263810779549</v>
+        <v>7.884452962611468</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.3</v>
+        <v>2.340833119445856</v>
       </c>
       <c r="JC93" t="n">
-        <v>2.183263894138653</v>
+        <v>7.884453045970572</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.3</v>
+        <v>2.340833119445856</v>
       </c>
       <c r="JC94" t="n">
-        <v>2.183263727420444</v>
+        <v>7.884452879252363</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.3</v>
+        <v>2.340833119445856</v>
       </c>
       <c r="JC95" t="n">
-        <v>2.183263916872954</v>
+        <v>7.884453068704874</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.3</v>
+        <v>2.340833119445856</v>
       </c>
       <c r="JC96" t="n">
-        <v>2.183263568280336</v>
+        <v>7.884452720112255</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.3</v>
+        <v>-1.260392056209815</v>
       </c>
       <c r="JC97" t="n">
-        <v>2.183263363671625</v>
+        <v>7.884452515503544</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.3</v>
+        <v>1.740833119445856</v>
       </c>
       <c r="JC98" t="n">
-        <v>2.183263477343131</v>
+        <v>7.88445262917505</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.3</v>
+        <v>1.740833119445856</v>
       </c>
       <c r="JC99" t="n">
-        <v>2.183263492499332</v>
+        <v>7.884452644331252</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.3</v>
+        <v>2.340833119445856</v>
       </c>
       <c r="JC100" t="n">
-        <v>2.18326325757822</v>
+        <v>7.884452409410139</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.3</v>
+        <v>2.340833119445856</v>
       </c>
       <c r="JC101" t="n">
-        <v>2.183263318203023</v>
+        <v>7.884452470034942</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.3</v>
+        <v>2.340833119445856</v>
       </c>
       <c r="JC102" t="n">
-        <v>2.183263189375316</v>
+        <v>7.884452341207236</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.3</v>
+        <v>2.340833119445856</v>
       </c>
       <c r="JC103" t="n">
-        <v>2.183263325781123</v>
+        <v>7.884452477613043</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.3</v>
+        <v>2.340833119445856</v>
       </c>
       <c r="JC104" t="n">
-        <v>2.183263500077433</v>
+        <v>7.884452651909351</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.3</v>
+        <v>-1.260392056209815</v>
       </c>
       <c r="JC105" t="n">
-        <v>2.18326364406134</v>
+        <v>7.884452795893259</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.3</v>
+        <v>1.740833119445856</v>
       </c>
       <c r="JC106" t="n">
-        <v>2.183263477343131</v>
+        <v>7.88445262917505</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>1</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.3</v>
+        <v>1.740833119445856</v>
       </c>
       <c r="JC107" t="n">
-        <v>2.183263469765031</v>
+        <v>7.884452621596951</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>1</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.3</v>
+        <v>2.340833119445856</v>
       </c>
       <c r="JC108" t="n">
-        <v>2.183263181797216</v>
+        <v>7.884452333629135</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.3</v>
+        <v>2.340833119445856</v>
       </c>
       <c r="JC109" t="n">
-        <v>2.183263196953417</v>
+        <v>7.884452348785335</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.3</v>
+        <v>2.340833119445856</v>
       </c>
       <c r="JC110" t="n">
-        <v>2.183263424296428</v>
+        <v>7.884452576128349</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.3</v>
+        <v>2.340833119445856</v>
       </c>
       <c r="JC111" t="n">
-        <v>2.183263409140228</v>
+        <v>7.884452560972147</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.3</v>
+        <v>-1.260392056209815</v>
       </c>
       <c r="JC112" t="n">
-        <v>2.183263515233633</v>
+        <v>7.884452667065553</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.3</v>
+        <v>-1.260392056209815</v>
       </c>
       <c r="JC113" t="n">
-        <v>2.183263242422019</v>
+        <v>7.884452394253938</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.3</v>
+        <v>-1.260392056209815</v>
       </c>
       <c r="JC114" t="n">
-        <v>2.183263340937324</v>
+        <v>7.884452492769243</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.3</v>
+        <v>1.740833119445856</v>
       </c>
       <c r="JC115" t="n">
-        <v>2.183263492499332</v>
+        <v>7.884452644331252</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.3</v>
+        <v>1.740833119445856</v>
       </c>
       <c r="JC116" t="n">
-        <v>2.183263507655533</v>
+        <v>7.884452659487453</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.3</v>
+        <v>2.340833119445856</v>
       </c>
       <c r="JC117" t="n">
-        <v>2.183263484921231</v>
+        <v>7.884452636753151</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.3</v>
+        <v>2.340833119445856</v>
       </c>
       <c r="JC118" t="n">
-        <v>2.183263568280336</v>
+        <v>7.884452720112255</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.3</v>
+        <v>-0.6603920562098147</v>
       </c>
       <c r="JC119" t="n">
-        <v>2.183263666795641</v>
+        <v>7.884452818627561</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.3</v>
+        <v>-1.260392056209815</v>
       </c>
       <c r="JC120" t="n">
-        <v>2.183263500077433</v>
+        <v>7.884452651909351</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.3</v>
+        <v>-1.260392056209815</v>
       </c>
       <c r="JC121" t="n">
-        <v>2.183263484921231</v>
+        <v>7.884452636753151</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.3</v>
+        <v>-1.260392056209815</v>
       </c>
       <c r="JC122" t="n">
-        <v>2.18326345460883</v>
+        <v>7.884452606440749</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.3</v>
+        <v>-1.260392056209815</v>
       </c>
       <c r="JC123" t="n">
-        <v>2.183263439452629</v>
+        <v>7.884452591284549</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.3</v>
+        <v>-1.260392056209815</v>
       </c>
       <c r="JC124" t="n">
-        <v>2.183263477343131</v>
+        <v>7.88445262917505</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.3</v>
+        <v>-1.260392056209815</v>
       </c>
       <c r="JC125" t="n">
-        <v>2.183263492499332</v>
+        <v>7.884452644331252</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.3</v>
+        <v>2.340833119445856</v>
       </c>
       <c r="JC126" t="n">
-        <v>2.183263484921231</v>
+        <v>7.884452636753151</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-S4_repeat_5_000007.xlsx
+++ b/out/Attention-S4_repeat_5_000007.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA6" t="n">
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA7" t="n">
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA8" t="n">
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA9" t="n">
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA10" t="n">
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA11" t="n">
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA12" t="n">
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA13" t="n">
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA15" t="n">
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA17" t="n">
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA18" t="n">
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA19" t="n">
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA20" t="n">
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA22" t="n">
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA23" t="n">
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA32" t="n">
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,17 +31942,17 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA39" t="n">
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC39" t="n">
-        <v>-7.712256331345998e-05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -32733,21 +32733,21 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>0.889109252280405</v>
+        <v>0</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA40" t="n">
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC40" t="n">
-        <v>1.779592907008404</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -33528,21 +33528,21 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.1333258984963202</v>
+        <v>0</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA41" t="n">
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC41" t="n">
-        <v>1.155942144807108</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -34323,21 +34323,21 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.1667007545622656</v>
+        <v>0</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA42" t="n">
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC42" t="n">
-        <v>1.356038928517799</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -35118,21 +35118,21 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.2389645784281521</v>
+        <v>0</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA43" t="n">
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC43" t="n">
-        <v>1.667361733030028</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -35913,21 +35913,21 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.2556451129256772</v>
+        <v>0</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA44" t="n">
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC44" t="n">
-        <v>1.939704871897068</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -36708,21 +36708,21 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.2709315542955592</v>
+        <v>0</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA45" t="n">
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC45" t="n">
-        <v>2.225943688836998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -37503,21 +37503,21 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1222670373213373</v>
+        <v>0</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA46" t="n">
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC46" t="n">
-        <v>2.19931958941948</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -38298,21 +38298,21 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.05904874746033055</v>
+        <v>0</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA47" t="n">
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC47" t="n">
-        <v>2.19505546025556</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -39093,21 +39093,21 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.02813558306727647</v>
+        <v>0</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA48" t="n">
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC48" t="n">
-        <v>2.192229698691393</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -39888,21 +39888,21 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.008333563627179606</v>
+        <v>0</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA49" t="n">
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC49" t="n">
-        <v>2.180734450292196</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -40683,21 +40683,21 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.005510641582937633</v>
+        <v>0</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA50" t="n">
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC50" t="n">
-        <v>2.18341892269172</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -41478,21 +41478,21 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.002817967231921131</v>
+        <v>0</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA51" t="n">
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC51" t="n">
-        <v>2.183540957973626</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -42273,21 +42273,21 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.001439560167255453</v>
+        <v>0</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA52" t="n">
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC52" t="n">
-        <v>2.183599447234295</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -43068,21 +43068,21 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0005376864856202011</v>
+        <v>0</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA53" t="n">
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC53" t="n">
-        <v>2.183234922977324</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -43863,21 +43863,21 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0002911771458358382</v>
+        <v>0</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA54" t="n">
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC54" t="n">
-        <v>2.183278531161338</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -44658,21 +44658,21 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0001372566611499408</v>
+        <v>0</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA55" t="n">
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC55" t="n">
-        <v>2.183262475273386</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -45453,21 +45453,21 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>8.355596056915365e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA56" t="n">
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC56" t="n">
-        <v>2.183291468911106</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -46248,21 +46248,21 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>4.132161208684532e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA57" t="n">
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC57" t="n">
-        <v>2.183290504722986</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -47043,21 +47043,21 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>1.698004887727391e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA58" t="n">
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC58" t="n">
-        <v>2.183284113910244</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -47838,21 +47838,21 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>9.070610155389825e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA59" t="n">
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC59" t="n">
-        <v>2.1832855457952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -48633,21 +48633,21 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>1.993667665820105e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA60" t="n">
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC60" t="n">
-        <v>2.18327917324003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -49428,21 +49428,21 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-1.911892527543644e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA61" t="n">
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC61" t="n">
-        <v>2.183273351047698</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -50223,21 +50223,21 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-3.887371769088796e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA62" t="n">
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC62" t="n">
-        <v>2.183268599772485</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -51018,21 +51018,21 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-4.031182895915095e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA63" t="n">
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC63" t="n">
-        <v>2.183263310624922</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -51817,17 +51817,17 @@
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA64" t="n">
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC64" t="n">
-        <v>2.183263287890621</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -52612,17 +52612,17 @@
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA65" t="n">
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC65" t="n">
-        <v>2.183263606170838</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -53407,17 +53407,17 @@
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA66" t="n">
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC66" t="n">
-        <v>2.183264697417295</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -54202,17 +54202,17 @@
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA67" t="n">
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC67" t="n">
-        <v>2.183264007810159</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -54997,17 +54997,17 @@
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA68" t="n">
         <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC68" t="n">
-        <v>2.183264038122561</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -55792,17 +55792,17 @@
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA69" t="n">
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC69" t="n">
-        <v>2.18326384867005</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -56587,17 +56587,17 @@
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA70" t="n">
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC70" t="n">
-        <v>2.183263901716753</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -57382,17 +57382,17 @@
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA71" t="n">
         <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC71" t="n">
-        <v>2.183263954763456</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -58177,17 +58177,17 @@
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA72" t="n">
         <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC72" t="n">
-        <v>2.183263916872954</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -58972,17 +58972,17 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA73" t="n">
         <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC73" t="n">
-        <v>2.183263788045247</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -59767,17 +59767,17 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA74" t="n">
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC74" t="n">
-        <v>2.18326364406134</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -60562,17 +60562,17 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA75" t="n">
         <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC75" t="n">
-        <v>2.183263484921231</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -61357,17 +61357,17 @@
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA76" t="n">
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC76" t="n">
-        <v>2.183263537967934</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -62152,17 +62152,17 @@
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA77" t="n">
         <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC77" t="n">
-        <v>2.183263484921231</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -62947,17 +62947,17 @@
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA78" t="n">
         <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC78" t="n">
-        <v>2.183263484921231</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -63742,17 +63742,17 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA79" t="n">
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC79" t="n">
-        <v>2.183263303046822</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -64537,17 +64537,17 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA80" t="n">
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC80" t="n">
-        <v>2.183263469765031</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -65332,17 +65332,17 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA81" t="n">
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC81" t="n">
-        <v>2.183263666795641</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -66127,17 +66127,17 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA82" t="n">
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC82" t="n">
-        <v>2.183263507655533</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -66922,17 +66922,17 @@
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA83" t="n">
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC83" t="n">
-        <v>2.183263545546035</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -67717,17 +67717,17 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA84" t="n">
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC84" t="n">
-        <v>2.183263742576645</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -68512,17 +68512,17 @@
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA85" t="n">
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC85" t="n">
-        <v>2.183263719842344</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -69307,17 +69307,17 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA86" t="n">
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC86" t="n">
-        <v>2.183263568280336</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -70102,17 +70102,17 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA87" t="n">
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC87" t="n">
-        <v>2.183263492499332</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -70897,17 +70897,17 @@
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA88" t="n">
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC88" t="n">
-        <v>2.183263591014637</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -71692,17 +71692,17 @@
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA89" t="n">
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC89" t="n">
-        <v>2.183263598592738</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -72487,17 +72487,17 @@
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA90" t="n">
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC90" t="n">
-        <v>2.183263863826252</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -73282,17 +73282,17 @@
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA91" t="n">
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC91" t="n">
-        <v>2.183263568280336</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -74077,17 +74077,17 @@
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA92" t="n">
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC92" t="n">
-        <v>2.183263810779549</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -74872,17 +74872,17 @@
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA93" t="n">
         <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC93" t="n">
-        <v>2.183263894138653</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -75667,17 +75667,17 @@
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA94" t="n">
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC94" t="n">
-        <v>2.183263727420444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -76462,17 +76462,17 @@
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA95" t="n">
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC95" t="n">
-        <v>2.183263916872954</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -77257,17 +77257,17 @@
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA96" t="n">
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC96" t="n">
-        <v>2.183263568280336</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -78052,17 +78052,17 @@
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA97" t="n">
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC97" t="n">
-        <v>2.183263363671625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -78847,17 +78847,17 @@
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA98" t="n">
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC98" t="n">
-        <v>2.183263477343131</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -79642,17 +79642,17 @@
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA99" t="n">
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC99" t="n">
-        <v>2.183263492499332</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -80437,17 +80437,17 @@
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA100" t="n">
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC100" t="n">
-        <v>2.18326325757822</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -81232,17 +81232,17 @@
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA101" t="n">
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC101" t="n">
-        <v>2.183263318203023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -82027,17 +82027,17 @@
       </c>
       <c r="IZ102" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA102" t="n">
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC102" t="n">
-        <v>2.183263189375316</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -82822,17 +82822,17 @@
       </c>
       <c r="IZ103" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA103" t="n">
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC103" t="n">
-        <v>2.183263325781123</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -83617,17 +83617,17 @@
       </c>
       <c r="IZ104" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA104" t="n">
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC104" t="n">
-        <v>2.183263500077433</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -84412,17 +84412,17 @@
       </c>
       <c r="IZ105" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA105" t="n">
         <v>1</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC105" t="n">
-        <v>2.18326364406134</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -85207,17 +85207,17 @@
       </c>
       <c r="IZ106" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA106" t="n">
         <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC106" t="n">
-        <v>2.183263477343131</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -86002,17 +86002,17 @@
       </c>
       <c r="IZ107" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA107" t="n">
         <v>1</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC107" t="n">
-        <v>2.183263469765031</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -86797,17 +86797,17 @@
       </c>
       <c r="IZ108" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA108" t="n">
         <v>1</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC108" t="n">
-        <v>2.183263181797216</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -87592,17 +87592,17 @@
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA109" t="n">
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC109" t="n">
-        <v>2.183263196953417</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -88387,17 +88387,17 @@
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA110" t="n">
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC110" t="n">
-        <v>2.183263424296428</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -89182,17 +89182,17 @@
       </c>
       <c r="IZ111" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA111" t="n">
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC111" t="n">
-        <v>2.183263409140228</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -89977,17 +89977,17 @@
       </c>
       <c r="IZ112" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA112" t="n">
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC112" t="n">
-        <v>2.183263515233633</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -90772,17 +90772,17 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA113" t="n">
         <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC113" t="n">
-        <v>2.183263242422019</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -91567,17 +91567,17 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA114" t="n">
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC114" t="n">
-        <v>2.183263340937324</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -92362,17 +92362,17 @@
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA115" t="n">
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC115" t="n">
-        <v>2.183263492499332</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -93157,17 +93157,17 @@
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA116" t="n">
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC116" t="n">
-        <v>2.183263507655533</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -93952,17 +93952,17 @@
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA117" t="n">
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC117" t="n">
-        <v>2.183263484921231</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -94747,17 +94747,17 @@
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA118" t="n">
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC118" t="n">
-        <v>2.183263568280336</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -95542,17 +95542,17 @@
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA119" t="n">
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC119" t="n">
-        <v>2.183263666795641</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
@@ -96337,17 +96337,17 @@
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA120" t="n">
         <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC120" t="n">
-        <v>2.183263500077433</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -97132,17 +97132,17 @@
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA121" t="n">
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC121" t="n">
-        <v>2.183263484921231</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -97927,17 +97927,17 @@
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA122" t="n">
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC122" t="n">
-        <v>2.18326345460883</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -98722,17 +98722,17 @@
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA123" t="n">
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC123" t="n">
-        <v>2.183263439452629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -99517,17 +99517,17 @@
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA124" t="n">
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC124" t="n">
-        <v>2.183263477343131</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -100312,17 +100312,17 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA125" t="n">
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC125" t="n">
-        <v>2.183263492499332</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -101103,21 +101103,21 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>-3.857095742388521e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
-          <t>Sell (Force)</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA126" t="n">
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC126" t="n">
-        <v>2.183263484921231</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-S4_repeat_5_000007.xlsx
+++ b/out/Attention-S4_repeat_5_000007.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0.01415656507015228</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.58</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.01287038251757622</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.58</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.01217161864042282</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.01352876797318459</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.009710408747196198</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0.01050150394439697</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0.01013414561748505</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0.01008471101522446</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.01058225333690643</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0.01005371659994125</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.00993683934211731</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0.009884588420391083</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.01004455983638763</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.009360082447528839</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.009898751974105835</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.009857490658760071</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.009829014539718628</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.009564965963363647</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.009827107191085815</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.01011305302381516</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.01026146858930588</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.01052939146757126</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.009629376232624054</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.01110237091779709</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.0113205686211586</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.01153389364480972</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.01195953786373138</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.01289524137973785</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.01196444034576416</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.01280797272920609</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.01302486285567284</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.01284541189670563</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.01348104700446129</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.01344471424818039</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.01595494523644447</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.02075096219778061</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.01224712282419205</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,17 +31942,17 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.0154406949877739</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC39" t="n">
-        <v>0</v>
+        <v>-0.0001198271120400168</v>
       </c>
     </row>
     <row r="40">
@@ -32733,21 +32733,21 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>0</v>
+        <v>1.381429628523334</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.01452765613794327</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC40" t="n">
-        <v>0</v>
+        <v>2.764994697947492</v>
       </c>
     </row>
     <row r="41">
@@ -33528,21 +33528,21 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0</v>
+        <v>0.2071515123543217</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.01596119254827499</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC41" t="n">
-        <v>0</v>
+        <v>1.796014070980345</v>
       </c>
     </row>
     <row r="42">
@@ -34323,21 +34323,21 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0</v>
+        <v>0.2590067931860441</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.01791775226593018</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC42" t="n">
-        <v>0</v>
+        <v>2.106909110305827</v>
       </c>
     </row>
     <row r="43">
@@ -35118,21 +35118,21 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0</v>
+        <v>0.3712850097179488</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.02551277726888657</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC43" t="n">
-        <v>0</v>
+        <v>2.590618717739739</v>
       </c>
     </row>
     <row r="44">
@@ -35913,21 +35913,21 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0</v>
+        <v>0.3972017644031713</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.02341747283935547</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC44" t="n">
-        <v>0</v>
+        <v>3.013764593845478</v>
       </c>
     </row>
     <row r="45">
@@ -36708,21 +36708,21 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0</v>
+        <v>0.4209538105437839</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.0222063772380352</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC45" t="n">
-        <v>0</v>
+        <v>3.458500506783282</v>
       </c>
     </row>
     <row r="46">
@@ -37503,21 +37503,21 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0</v>
+        <v>0.189967959610658</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.02405938506126404</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC46" t="n">
-        <v>0</v>
+        <v>3.417134137252217</v>
       </c>
     </row>
     <row r="47">
@@ -38298,21 +38298,21 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0</v>
+        <v>0.09174584171355227</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.008990228176116943</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC47" t="n">
-        <v>0</v>
+        <v>3.410508854761834</v>
       </c>
     </row>
     <row r="48">
@@ -39093,21 +39093,21 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0</v>
+        <v>0.04371416212892491</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.02145040780305862</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>0</v>
+        <v>3.406118417763512</v>
       </c>
     </row>
     <row r="49">
@@ -39888,21 +39888,21 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0</v>
+        <v>0.01295116312619724</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.01268438994884491</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>0</v>
+        <v>3.388260556076216</v>
       </c>
     </row>
     <row r="50">
@@ -40683,21 +40683,21 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0</v>
+        <v>0.008565488036506088</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.01983559876680374</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC50" t="n">
-        <v>0</v>
+        <v>3.392434231809489</v>
       </c>
     </row>
     <row r="51">
@@ -41478,21 +41478,21 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0</v>
+        <v>0.00438147191352541</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.01736205071210861</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC51" t="n">
-        <v>0</v>
+        <v>3.392626590449161</v>
       </c>
     </row>
     <row r="52">
@@ -42273,21 +42273,21 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0</v>
+        <v>0.002238849904398888</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.01998813077807426</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC52" t="n">
-        <v>0</v>
+        <v>3.392720208959288</v>
       </c>
     </row>
     <row r="53">
@@ -43068,21 +43068,21 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0</v>
+        <v>0.0008381697977418467</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.0137825608253479</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>0</v>
+        <v>3.392156756042171</v>
       </c>
     </row>
     <row r="54">
@@ -43863,21 +43863,21 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0</v>
+        <v>0.0004545283293330415</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.01070735603570938</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC54" t="n">
-        <v>0</v>
+        <v>3.392227241399659</v>
       </c>
     </row>
     <row r="55">
@@ -44658,21 +44658,21 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0</v>
+        <v>0.0002167296562057736</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.01095874607563019</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>0</v>
+        <v>3.392205056284695</v>
       </c>
     </row>
     <row r="56">
@@ -45453,21 +45453,21 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0</v>
+        <v>0.0001317697613234706</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.01196586340665817</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC56" t="n">
-        <v>0</v>
+        <v>3.39225274702213</v>
       </c>
     </row>
     <row r="57">
@@ -46248,21 +46248,21 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0</v>
+        <v>6.705584102398162e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.01412317901849747</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC57" t="n">
-        <v>0</v>
+        <v>3.392254024951721</v>
       </c>
     </row>
     <row r="58">
@@ -47043,21 +47043,21 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0</v>
+        <v>2.996825957748122e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.02416857704520226</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC58" t="n">
-        <v>0</v>
+        <v>3.39224686051936</v>
       </c>
     </row>
     <row r="59">
@@ -47838,21 +47838,21 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0</v>
+        <v>1.67454884219661e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.01357635483145714</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC59" t="n">
-        <v>0</v>
+        <v>3.392251647765358</v>
       </c>
     </row>
     <row r="60">
@@ -48633,21 +48633,21 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0</v>
+        <v>5.490501498730158e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.01113008707761765</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC60" t="n">
-        <v>0</v>
+        <v>3.392244588932602</v>
       </c>
     </row>
     <row r="61">
@@ -49428,21 +49428,21 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0</v>
+        <v>-8.825233700581938e-07</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.01276911050081253</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>0</v>
+        <v>3.392238356270352</v>
       </c>
     </row>
     <row r="62">
@@ -50223,21 +50223,21 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0</v>
+        <v>-2.77474353817759e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.01171894371509552</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC62" t="n">
-        <v>0</v>
+        <v>3.39223377036082</v>
       </c>
     </row>
     <row r="63">
@@ -51018,21 +51018,21 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0</v>
+        <v>-4.031182895915095e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0.01294674724340439</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="JC63" t="n">
-        <v>0</v>
+        <v>3.392228337229351</v>
       </c>
     </row>
     <row r="64">
@@ -51813,21 +51813,21 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0</v>
+        <v>-4.053889915940302e-06</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0.02023158222436905</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC64" t="n">
-        <v>0</v>
+        <v>3.392223290608284</v>
       </c>
     </row>
     <row r="65">
@@ -52612,17 +52612,17 @@
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.02730186283588409</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>0</v>
+        <v>3.3922236088885</v>
       </c>
     </row>
     <row r="66">
@@ -53407,17 +53407,17 @@
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.03033139929175377</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>0</v>
+        <v>3.392224700134957</v>
       </c>
     </row>
     <row r="67">
@@ -54202,17 +54202,17 @@
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.01796974986791611</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC67" t="n">
-        <v>0</v>
+        <v>3.392224010527821</v>
       </c>
     </row>
     <row r="68">
@@ -54997,17 +54997,17 @@
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0.01477134227752686</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="JC68" t="n">
-        <v>0</v>
+        <v>3.392224040840223</v>
       </c>
     </row>
     <row r="69">
@@ -55792,17 +55792,17 @@
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.01603950187563896</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="JC69" t="n">
-        <v>0</v>
+        <v>3.392223851387713</v>
       </c>
     </row>
     <row r="70">
@@ -56587,17 +56587,17 @@
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0.01901461556553841</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC70" t="n">
-        <v>0</v>
+        <v>3.392223904434416</v>
       </c>
     </row>
     <row r="71">
@@ -57382,17 +57382,17 @@
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0.02258259430527687</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC71" t="n">
-        <v>0</v>
+        <v>3.392223957481119</v>
       </c>
     </row>
     <row r="72">
@@ -58177,17 +58177,17 @@
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0.02658853307366371</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC72" t="n">
-        <v>0</v>
+        <v>3.392223919590617</v>
       </c>
     </row>
     <row r="73">
@@ -58972,17 +58972,17 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0.009253911674022675</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>0</v>
+        <v>3.39222379076291</v>
       </c>
     </row>
     <row r="74">
@@ -59767,17 +59767,17 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.007541760802268982</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC74" t="n">
-        <v>0</v>
+        <v>3.392223646779003</v>
       </c>
     </row>
     <row r="75">
@@ -60562,17 +60562,17 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0.009124524891376495</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>0</v>
+        <v>3.392223487638895</v>
       </c>
     </row>
     <row r="76">
@@ -61357,17 +61357,17 @@
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0.006977386772632599</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>0</v>
+        <v>3.392223540685597</v>
       </c>
     </row>
     <row r="77">
@@ -62152,17 +62152,17 @@
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0.01012019068002701</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC77" t="n">
-        <v>0</v>
+        <v>3.392223487638895</v>
       </c>
     </row>
     <row r="78">
@@ -62947,17 +62947,17 @@
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0.01206584274768829</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC78" t="n">
-        <v>0</v>
+        <v>3.392223487638895</v>
       </c>
     </row>
     <row r="79">
@@ -63742,17 +63742,17 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0.01747101917862892</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC79" t="n">
-        <v>0</v>
+        <v>3.392223305764485</v>
       </c>
     </row>
     <row r="80">
@@ -64537,17 +64537,17 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.01751795038580894</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC80" t="n">
-        <v>0</v>
+        <v>3.392223472482693</v>
       </c>
     </row>
     <row r="81">
@@ -65332,17 +65332,17 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0.01406696811318398</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="JC81" t="n">
-        <v>0</v>
+        <v>3.392223669513304</v>
       </c>
     </row>
     <row r="82">
@@ -66127,17 +66127,17 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.01169098913669586</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>0</v>
+        <v>3.392223510373196</v>
       </c>
     </row>
     <row r="83">
@@ -66922,17 +66922,17 @@
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.01300834119319916</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC83" t="n">
-        <v>0</v>
+        <v>3.392223548263697</v>
       </c>
     </row>
     <row r="84">
@@ -67717,17 +67717,17 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.01377904042601585</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC84" t="n">
-        <v>0</v>
+        <v>3.392223745294307</v>
       </c>
     </row>
     <row r="85">
@@ -68512,17 +68512,17 @@
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.01345082744956017</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC85" t="n">
-        <v>0</v>
+        <v>3.392223722560006</v>
       </c>
     </row>
     <row r="86">
@@ -69307,17 +69307,17 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.01117661595344543</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC86" t="n">
-        <v>0</v>
+        <v>3.392223570997998</v>
       </c>
     </row>
     <row r="87">
@@ -70102,17 +70102,17 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.01135612279176712</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>0</v>
+        <v>3.392223495216995</v>
       </c>
     </row>
     <row r="88">
@@ -70897,17 +70897,17 @@
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.014412522315979</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>0</v>
+        <v>3.3922235937323</v>
       </c>
     </row>
     <row r="89">
@@ -71692,17 +71692,17 @@
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.01876910775899887</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>0</v>
+        <v>3.3922236013104</v>
       </c>
     </row>
     <row r="90">
@@ -72487,17 +72487,17 @@
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.01490577682852745</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC90" t="n">
-        <v>0</v>
+        <v>3.392223866543914</v>
       </c>
     </row>
     <row r="91">
@@ -73282,17 +73282,17 @@
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.01130973547697067</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>0</v>
+        <v>3.392223570997998</v>
       </c>
     </row>
     <row r="92">
@@ -74077,17 +74077,17 @@
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.01445869356393814</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC92" t="n">
-        <v>0</v>
+        <v>3.392223813497211</v>
       </c>
     </row>
     <row r="93">
@@ -74872,17 +74872,17 @@
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0.01154522597789764</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC93" t="n">
-        <v>0</v>
+        <v>3.392223896856315</v>
       </c>
     </row>
     <row r="94">
@@ -75667,17 +75667,17 @@
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.01609217748045921</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>0</v>
+        <v>3.392223730138107</v>
       </c>
     </row>
     <row r="95">
@@ -76462,17 +76462,17 @@
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0.01004263013601303</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>0</v>
+        <v>3.392223919590617</v>
       </c>
     </row>
     <row r="96">
@@ -77257,17 +77257,17 @@
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.01417659223079681</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>0</v>
+        <v>3.392223570997998</v>
       </c>
     </row>
     <row r="97">
@@ -78052,17 +78052,17 @@
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0.01207674294710159</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>0</v>
+        <v>3.392223366389288</v>
       </c>
     </row>
     <row r="98">
@@ -78847,17 +78847,17 @@
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0.01000799983739853</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>0</v>
+        <v>3.392223480060793</v>
       </c>
     </row>
     <row r="99">
@@ -79642,17 +79642,17 @@
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0.009093441069126129</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC99" t="n">
-        <v>0</v>
+        <v>3.392223495216995</v>
       </c>
     </row>
     <row r="100">
@@ -80437,17 +80437,17 @@
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.009290054440498352</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC100" t="n">
-        <v>0</v>
+        <v>3.392223260295883</v>
       </c>
     </row>
     <row r="101">
@@ -81232,17 +81232,17 @@
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.008879303932189941</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>0</v>
+        <v>3.392223320920685</v>
       </c>
     </row>
     <row r="102">
@@ -82027,17 +82027,17 @@
       </c>
       <c r="IZ102" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.01132974028587341</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>0</v>
+        <v>3.392223192092978</v>
       </c>
     </row>
     <row r="103">
@@ -82822,17 +82822,17 @@
       </c>
       <c r="IZ103" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.01280425116419792</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>0</v>
+        <v>3.392223328498786</v>
       </c>
     </row>
     <row r="104">
@@ -83617,17 +83617,17 @@
       </c>
       <c r="IZ104" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0.009520582854747772</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>0</v>
+        <v>3.392223502795094</v>
       </c>
     </row>
     <row r="105">
@@ -84412,17 +84412,17 @@
       </c>
       <c r="IZ105" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0.01094358414411545</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>0</v>
+        <v>3.392223646779003</v>
       </c>
     </row>
     <row r="106">
@@ -85207,17 +85207,17 @@
       </c>
       <c r="IZ106" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0.01000569760799408</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC106" t="n">
-        <v>0</v>
+        <v>3.392223480060793</v>
       </c>
     </row>
     <row r="107">
@@ -86002,17 +86002,17 @@
       </c>
       <c r="IZ107" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0.01041597872972488</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC107" t="n">
-        <v>0</v>
+        <v>3.392223472482693</v>
       </c>
     </row>
     <row r="108">
@@ -86797,17 +86797,17 @@
       </c>
       <c r="IZ108" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0.008724503219127655</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC108" t="n">
-        <v>0</v>
+        <v>3.392223184514878</v>
       </c>
     </row>
     <row r="109">
@@ -87592,17 +87592,17 @@
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.009851813316345215</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>0</v>
+        <v>3.392223199671079</v>
       </c>
     </row>
     <row r="110">
@@ -88387,17 +88387,17 @@
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0.01072560995817184</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC110" t="n">
-        <v>0</v>
+        <v>3.392223427014091</v>
       </c>
     </row>
     <row r="111">
@@ -89182,17 +89182,17 @@
       </c>
       <c r="IZ111" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.01085681468248367</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC111" t="n">
-        <v>0</v>
+        <v>3.39222341185789</v>
       </c>
     </row>
     <row r="112">
@@ -89977,17 +89977,17 @@
       </c>
       <c r="IZ112" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.01022131741046906</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC112" t="n">
-        <v>0</v>
+        <v>3.392223517951296</v>
       </c>
     </row>
     <row r="113">
@@ -90772,17 +90772,17 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0.009971864521503448</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>0</v>
+        <v>3.392223245139682</v>
       </c>
     </row>
     <row r="114">
@@ -91567,17 +91567,17 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.009879522025585175</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>0</v>
+        <v>3.392223343654987</v>
       </c>
     </row>
     <row r="115">
@@ -92362,17 +92362,17 @@
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.009903661906719208</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC115" t="n">
-        <v>0</v>
+        <v>3.392223495216995</v>
       </c>
     </row>
     <row r="116">
@@ -93157,17 +93157,17 @@
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.010328508913517</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC116" t="n">
-        <v>0</v>
+        <v>3.392223510373196</v>
       </c>
     </row>
     <row r="117">
@@ -93952,17 +93952,17 @@
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.009987220168113708</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC117" t="n">
-        <v>0</v>
+        <v>3.392223487638895</v>
       </c>
     </row>
     <row r="118">
@@ -94747,17 +94747,17 @@
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.009901918470859528</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC118" t="n">
-        <v>0</v>
+        <v>3.392223570997998</v>
       </c>
     </row>
     <row r="119">
@@ -95542,17 +95542,17 @@
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.009554475545883179</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC119" t="n">
-        <v>0</v>
+        <v>3.392223669513304</v>
       </c>
     </row>
     <row r="120">
@@ -96337,17 +96337,17 @@
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0.009589217603206635</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC120" t="n">
-        <v>0</v>
+        <v>3.392223502795094</v>
       </c>
     </row>
     <row r="121">
@@ -97132,17 +97132,17 @@
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.009673215448856354</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC121" t="n">
-        <v>0</v>
+        <v>3.392223487638895</v>
       </c>
     </row>
     <row r="122">
@@ -97927,17 +97927,17 @@
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0.009891629219055176</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>0</v>
+        <v>3.392223457326492</v>
       </c>
     </row>
     <row r="123">
@@ -98722,17 +98722,17 @@
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.01008133590221405</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC123" t="n">
-        <v>0</v>
+        <v>3.392223442170292</v>
       </c>
     </row>
     <row r="124">
@@ -99517,17 +99517,17 @@
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0.01026494055986404</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC124" t="n">
-        <v>0</v>
+        <v>3.392223480060793</v>
       </c>
     </row>
     <row r="125">
@@ -100312,17 +100312,17 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.01064114272594452</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1600000000000003</v>
       </c>
       <c r="JC125" t="n">
-        <v>0</v>
+        <v>3.392223495216995</v>
       </c>
     </row>
     <row r="126">
@@ -101103,21 +101103,21 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>0</v>
+        <v>-3.857095742388521e-06</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell (Force)</t>
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.009384043514728546</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3000000000000004</v>
       </c>
       <c r="JC126" t="n">
-        <v>0</v>
+        <v>3.392223487638895</v>
       </c>
     </row>
   </sheetData>
